--- a/data/trans_dic/IP18A01-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP18A01-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación</t>
+          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 18,79</t>
+          <t>7,16; 17,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,58; 21,98</t>
+          <t>8,77; 21,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 14,49</t>
+          <t>4,18; 14,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,51</t>
+          <t>0,0; 18,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 15,75</t>
+          <t>4,91; 15,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 14,97</t>
+          <t>4,33; 15,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 14,57</t>
+          <t>5,17; 15,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,14</t>
+          <t>0,0; 20,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,28; 15,31</t>
+          <t>7,31; 14,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,59; 15,36</t>
+          <t>7,41; 15,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 12,6</t>
+          <t>5,67; 12,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 14,56</t>
+          <t>1,53; 14,6</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 14,27</t>
+          <t>4,31; 14,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 13,69</t>
+          <t>4,09; 14,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,73; 17,65</t>
+          <t>6,36; 17,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 15,68</t>
+          <t>5,05; 16,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 18,41</t>
+          <t>7,11; 19,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 14,87</t>
+          <t>5,18; 15,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,41; 12,68</t>
+          <t>5,49; 12,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,86; 14,16</t>
+          <t>6,93; 14,22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,1; 14,12</t>
+          <t>7,06; 14,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 12,74</t>
+          <t>2,4; 13,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 16,87</t>
+          <t>5,92; 17,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 17,77</t>
+          <t>5,41; 18,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,74</t>
+          <t>0,0; 72,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 11,65</t>
+          <t>3,12; 11,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 14,61</t>
+          <t>3,98; 14,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 21,5</t>
+          <t>7,69; 22,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,88</t>
+          <t>0,0; 16,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 10,27</t>
+          <t>3,62; 10,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,28; 13,73</t>
+          <t>6,07; 13,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,03; 17,75</t>
+          <t>7,73; 17,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,49</t>
+          <t>0,0; 27,47</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 13,46</t>
+          <t>6,13; 13,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 14,3</t>
+          <t>6,85; 14,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,54; 12,24</t>
+          <t>6,05; 12,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 23,7</t>
+          <t>3,68; 21,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,18; 13,2</t>
+          <t>6,22; 12,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,01; 13,91</t>
+          <t>6,82; 13,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 14,59</t>
+          <t>6,78; 14,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 9,76</t>
+          <t>0,91; 10,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,26; 12,27</t>
+          <t>6,92; 12,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 12,87</t>
+          <t>7,95; 12,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 12,08</t>
+          <t>7,28; 12,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 12,67</t>
+          <t>2,76; 12,49</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 15,98</t>
+          <t>5,48; 16,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,74; 12,35</t>
+          <t>4,89; 12,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 11,87</t>
+          <t>4,52; 12,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,51</t>
+          <t>0,0; 12,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 11,21</t>
+          <t>2,78; 10,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,84; 16,3</t>
+          <t>6,91; 16,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,14</t>
+          <t>1,03; 6,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 13,25</t>
+          <t>1,21; 13,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,01; 11,51</t>
+          <t>4,97; 11,69</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,84; 12,89</t>
+          <t>6,73; 12,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 7,94</t>
+          <t>3,13; 7,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 10,28</t>
+          <t>1,49; 9,71</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 9,57</t>
+          <t>0,91; 9,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,0; 17,93</t>
+          <t>3,95; 18,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,39; 26,5</t>
+          <t>8,64; 25,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,84</t>
+          <t>0,0; 39,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,88; 18,47</t>
+          <t>6,05; 18,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,31; 17,84</t>
+          <t>4,82; 17,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,48; 15,45</t>
+          <t>3,51; 16,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,39; 12,06</t>
+          <t>4,4; 11,9</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,93; 14,63</t>
+          <t>6,07; 14,79</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,49; 18,15</t>
+          <t>7,66; 18,27</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,33</t>
+          <t>0,0; 19,59</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,96; 10,89</t>
+          <t>6,9; 10,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,87; 11,9</t>
+          <t>8,09; 12,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,96; 11,93</t>
+          <t>7,69; 11,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,74; 12,46</t>
+          <t>3,89; 12,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,71; 10,41</t>
+          <t>6,78; 10,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,31; 12,18</t>
+          <t>8,22; 12,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,96; 10,63</t>
+          <t>6,95; 10,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 7,2</t>
+          <t>1,62; 6,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,08</t>
+          <t>7,34; 10,04</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,74; 11,51</t>
+          <t>8,6; 11,55</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,84; 10,47</t>
+          <t>7,88; 10,54</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,24</t>
+          <t>3,04; 7,75</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>11158</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11205</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6021</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8237</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7450</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>8523</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>19395</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>18655</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14544</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2754</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>6764; 16976</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7154; 17286</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3148; 11180</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4528</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4225; 13688</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3720; 12920</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4807; 14077</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4134</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>13199; 26328</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>12408; 26257</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9535; 21233</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>693; 6615</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>6675</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7169</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10815</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6897</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10625</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9172</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>13571</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>17794</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>19988</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3463; 11720</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3659; 13389</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6129; 16558</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3807; 12173</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6281; 16998</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5112; 14891</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>8543; 19468</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>12321; 25277</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>13772; 27951</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4168</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8730</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5524</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5355</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6607</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>9283</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>9523</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>15337</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>14807</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1442; 8033</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4774; 14027</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2862; 9929</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2485</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2671; 10016</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3306; 11689</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5194; 14848</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 1759</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>5272; 15572</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9926; 22244</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>9316; 21260</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>15975</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19727</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18179</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3106</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16236</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>21993</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>19386</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1447</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>32211</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>41720</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>37564</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>4553</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>10577; 23116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>13182; 27447</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>12424; 26263</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1113; 6432</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>10980; 22411</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>14704; 29400</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>12775; 26638</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>373; 4360</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>24153; 42484</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>32428; 51870</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>28669; 48206</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1972; 8912</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>8158</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11013</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9146</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6113</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>14395</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3518</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1476</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>14271</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>25409</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>12665</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2218</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4703; 13760</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6667; 17064</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5547; 15167</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2523</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2854; 11189</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>9094; 21392</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1309; 8116</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>361; 4005</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>9377; 22041</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>18028; 33763</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>7820; 19233</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>750; 4889</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2638</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4885</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9233</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1201</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>7426</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>7126</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4982</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>10064</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>12011</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>14215</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1201</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>627; 6278</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2078; 9739</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>4863; 14577</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3691</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>4013; 12342</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>3352; 12049</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2142; 9954</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>5944; 16086</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>7415; 18072</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>8979; 21427</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4119</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>48772</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>62729</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>58918</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>50263</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>68196</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>54864</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>4687</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>99035</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>130924</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>113782</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>11846</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>38759; 59739</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>51221; 76433</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>46851; 71498</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>3843; 12529</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>40144; 62322</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>55397; 82137</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>44185; 67000</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2118; 8433</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>84718; 115942</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>112350; 150877</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>98097; 131190</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>6973; 17761</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A01-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP18A01-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 17,96</t>
+          <t>7,26; 18,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,77; 21,19</t>
+          <t>7,5; 20,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,18; 14,84</t>
+          <t>3,7; 15,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,28</t>
+          <t>0,0; 21,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 15,89</t>
+          <t>5,16; 15,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 15,05</t>
+          <t>4,32; 15,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 15,14</t>
+          <t>5,27; 15,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,13</t>
+          <t>0,0; 22,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 14,58</t>
+          <t>7,46; 15,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,41; 15,68</t>
+          <t>7,16; 15,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,67; 12,62</t>
+          <t>5,57; 13,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,6</t>
+          <t>1,84; 14,73</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,31; 14,6</t>
+          <t>4,42; 14,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 14,97</t>
+          <t>4,06; 14,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,36; 17,17</t>
+          <t>6,58; 17,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,17 +877,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,05; 16,15</t>
+          <t>5,19; 16,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,11; 19,25</t>
+          <t>7,16; 18,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 15,1</t>
+          <t>5,22; 14,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,49; 12,51</t>
+          <t>5,75; 13,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,93; 14,22</t>
+          <t>6,83; 14,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,06; 14,33</t>
+          <t>7,32; 14,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 13,37</t>
+          <t>2,61; 14,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,92; 17,39</t>
+          <t>5,86; 17,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 18,75</t>
+          <t>5,38; 18,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,77</t>
+          <t>0,0; 74,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 11,72</t>
+          <t>3,08; 11,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 14,08</t>
+          <t>3,96; 14,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,69; 22,0</t>
+          <t>7,42; 21,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,1</t>
+          <t>0,0; 20,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 10,7</t>
+          <t>3,84; 11,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,07; 13,59</t>
+          <t>6,09; 13,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 17,65</t>
+          <t>7,86; 17,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,47</t>
+          <t>0,0; 27,06</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,13; 13,41</t>
+          <t>6,2; 13,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 14,27</t>
+          <t>7,05; 14,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,05; 12,78</t>
+          <t>5,86; 12,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 21,3</t>
+          <t>3,68; 21,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 12,7</t>
+          <t>6,49; 12,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 13,64</t>
+          <t>7,37; 14,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,78; 14,13</t>
+          <t>7,24; 14,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 10,6</t>
+          <t>0,0; 9,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 12,18</t>
+          <t>6,85; 12,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,95; 12,72</t>
+          <t>8,03; 12,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 12,24</t>
+          <t>7,34; 12,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 12,49</t>
+          <t>2,73; 12,99</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,48; 16,03</t>
+          <t>5,49; 15,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,89; 12,52</t>
+          <t>5,02; 13,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,52; 12,37</t>
+          <t>4,5; 12,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,34</t>
+          <t>0,0; 13,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 10,89</t>
+          <t>3,22; 11,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,91; 16,25</t>
+          <t>6,67; 16,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,36</t>
+          <t>1,03; 6,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 13,39</t>
+          <t>1,27; 13,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,97; 11,69</t>
+          <t>4,94; 11,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,73; 12,6</t>
+          <t>6,77; 13,1</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,13; 7,69</t>
+          <t>3,08; 7,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 9,71</t>
+          <t>1,63; 10,68</t>
         </is>
       </c>
     </row>
@@ -1417,37 +1417,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 9,13</t>
+          <t>1,08; 9,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,95; 18,49</t>
+          <t>3,89; 18,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,64; 25,89</t>
+          <t>8,72; 27,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,45</t>
+          <t>0,0; 38,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,05; 18,59</t>
+          <t>6,02; 18,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,82; 17,33</t>
+          <t>5,24; 16,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,51; 16,33</t>
+          <t>3,43; 15,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1457,22 +1457,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,4; 11,9</t>
+          <t>4,45; 11,74</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,07; 14,79</t>
+          <t>5,97; 15,24</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,66; 18,27</t>
+          <t>7,7; 18,16</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,59</t>
+          <t>0,0; 19,53</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,9; 10,63</t>
+          <t>6,95; 10,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,09; 12,08</t>
+          <t>8,11; 12,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,69; 11,74</t>
+          <t>7,82; 11,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,89; 12,7</t>
+          <t>3,89; 12,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,78; 10,52</t>
+          <t>6,84; 10,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,22; 12,19</t>
+          <t>8,42; 12,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,95; 10,53</t>
+          <t>6,93; 10,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,47</t>
+          <t>1,75; 7,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,34; 10,04</t>
+          <t>7,27; 9,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,6; 11,55</t>
+          <t>8,73; 11,39</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,88; 10,54</t>
+          <t>7,75; 10,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,75</t>
+          <t>3,19; 8,1</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6764; 16976</t>
+          <t>6858; 17024</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7154; 17286</t>
+          <t>6115; 16992</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3148; 11180</t>
+          <t>2787; 11476</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4528</t>
+          <t>0; 5278</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4225; 13688</t>
+          <t>4447; 13212</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3720; 12920</t>
+          <t>3710; 13123</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4807; 14077</t>
+          <t>4894; 14163</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4134</t>
+          <t>0; 4677</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13199; 26328</t>
+          <t>13472; 27347</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12408; 26257</t>
+          <t>11994; 26612</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9535; 21233</t>
+          <t>9367; 22129</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>693; 6615</t>
+          <t>832; 6676</t>
         </is>
       </c>
     </row>
@@ -2135,17 +2135,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3463; 11720</t>
+          <t>3546; 11325</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3659; 13389</t>
+          <t>3632; 12620</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6129; 16558</t>
+          <t>6345; 17284</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2155,17 +2155,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3807; 12173</t>
+          <t>3912; 12382</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6281; 16998</t>
+          <t>6320; 16399</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5112; 14891</t>
+          <t>5146; 14469</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2175,17 +2175,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8543; 19468</t>
+          <t>8956; 20470</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12321; 25277</t>
+          <t>12140; 25378</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13772; 27951</t>
+          <t>14283; 27664</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1442; 8033</t>
+          <t>1566; 8831</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4774; 14027</t>
+          <t>4727; 14116</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2862; 9929</t>
+          <t>2847; 9802</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2485</t>
+          <t>0; 2536</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2671; 10016</t>
+          <t>2630; 10054</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3306; 11689</t>
+          <t>3287; 12142</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5194; 14848</t>
+          <t>5008; 14433</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 1759</t>
+          <t>0; 2221</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5272; 15572</t>
+          <t>5594; 16174</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9926; 22244</t>
+          <t>9962; 22063</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9316; 21260</t>
+          <t>9467; 20972</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3940</t>
+          <t>0; 3881</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10577; 23116</t>
+          <t>10694; 22525</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13182; 27447</t>
+          <t>13562; 27520</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12424; 26263</t>
+          <t>12048; 25638</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1113; 6432</t>
+          <t>1111; 6567</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10980; 22411</t>
+          <t>11456; 22813</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14704; 29400</t>
+          <t>15879; 30385</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12775; 26638</t>
+          <t>13636; 27442</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>373; 4360</t>
+          <t>0; 3865</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24153; 42484</t>
+          <t>23901; 42702</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32428; 51870</t>
+          <t>32735; 52815</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28669; 48206</t>
+          <t>28899; 47328</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1972; 8912</t>
+          <t>1945; 9263</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4703; 13760</t>
+          <t>4710; 13579</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6667; 17064</t>
+          <t>6842; 17756</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5547; 15167</t>
+          <t>5513; 15054</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2523</t>
+          <t>0; 2711</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2854; 11189</t>
+          <t>3303; 11400</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9094; 21392</t>
+          <t>8782; 21793</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1309; 8116</t>
+          <t>1317; 7972</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>361; 4005</t>
+          <t>381; 3975</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9377; 22041</t>
+          <t>9322; 21328</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18028; 33763</t>
+          <t>18136; 35099</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7820; 19233</t>
+          <t>7695; 19143</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>750; 4889</t>
+          <t>820; 5375</t>
         </is>
       </c>
     </row>
@@ -2967,37 +2967,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>627; 6278</t>
+          <t>743; 6443</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2078; 9739</t>
+          <t>2048; 9811</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4863; 14577</t>
+          <t>4909; 15497</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3691</t>
+          <t>0; 3626</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4013; 12342</t>
+          <t>3995; 12144</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3352; 12049</t>
+          <t>3643; 11558</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2142; 9954</t>
+          <t>2092; 9658</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3007,22 +3007,22 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5944; 16086</t>
+          <t>6012; 15864</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7415; 18072</t>
+          <t>7288; 18618</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8979; 21427</t>
+          <t>9032; 21299</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 4119</t>
+          <t>0; 4106</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>38759; 59739</t>
+          <t>39060; 60277</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>51221; 76433</t>
+          <t>51326; 76480</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46851; 71498</t>
+          <t>47630; 71930</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3843; 12529</t>
+          <t>3839; 12035</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>40144; 62322</t>
+          <t>40555; 62147</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>55397; 82137</t>
+          <t>56715; 82447</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44185; 67000</t>
+          <t>44074; 67025</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2118; 8433</t>
+          <t>2281; 9189</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>84718; 115942</t>
+          <t>83884; 113481</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>112350; 150877</t>
+          <t>114088; 148906</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>98097; 131190</t>
+          <t>96503; 130409</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6973; 17761</t>
+          <t>7314; 18544</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A01-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP18A01-Clase-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
+          <t>Menores cuya última consulta médica fue por vacunación (tasa de respuesta: 98,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9,56%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>11,81%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>13,74%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7,99%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,56%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 18,01</t>
+          <t>4,86; 15,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,5; 20,83</t>
+          <t>4,81; 14,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 15,23</t>
+          <t>4,72; 14,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,31</t>
+          <t>0,0; 24,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 15,34</t>
+          <t>7,14; 18,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 15,28</t>
+          <t>8,58; 21,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 15,24</t>
+          <t>4,06; 14,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,77</t>
+          <t>0,0; 26,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 15,14</t>
+          <t>7,28; 15,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 15,89</t>
+          <t>7,59; 15,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 13,15</t>
+          <t>5,48; 12,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 14,73</t>
+          <t>1,95; 16,8</t>
         </is>
       </c>
     </row>
@@ -789,37 +789,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9,15%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12,03%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>8,31%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>8,02%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>11,22%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,03%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 14,11</t>
+          <t>4,59; 15,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 14,11</t>
+          <t>7,01; 18,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,58; 17,92</t>
+          <t>5,01; 14,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,17 +877,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,19; 16,43</t>
+          <t>4,49; 14,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 18,57</t>
+          <t>3,91; 13,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,22; 14,67</t>
+          <t>6,73; 17,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,75; 13,15</t>
+          <t>5,41; 12,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 14,28</t>
+          <t>6,86; 14,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 14,18</t>
+          <t>7,1; 14,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,26%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13,75%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,94%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10,82%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>10,43%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22,34%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,75%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 14,7</t>
+          <t>3,08; 11,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 17,5</t>
+          <t>3,59; 14,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 18,51</t>
+          <t>7,56; 21,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,27</t>
+          <t>0,0; 12,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 11,76</t>
+          <t>2,4; 12,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,96; 14,63</t>
+          <t>6,0; 16,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,42; 21,38</t>
+          <t>5,19; 17,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,32</t>
+          <t>0,0; 78,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 11,11</t>
+          <t>3,6; 10,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,09; 13,48</t>
+          <t>6,28; 13,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,86; 17,41</t>
+          <t>8,03; 17,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,06</t>
+          <t>0,0; 30,52</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10,29%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9,26%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,26%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>8,85%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10,28%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,2%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,2; 13,06</t>
+          <t>6,18; 13,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 14,31</t>
+          <t>7,01; 13,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 12,48</t>
+          <t>7,29; 14,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 21,74</t>
+          <t>0,73; 9,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,49; 12,93</t>
+          <t>6,47; 13,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 14,1</t>
+          <t>6,8; 14,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 14,56</t>
+          <t>5,54; 12,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,4</t>
+          <t>3,67; 23,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 12,24</t>
+          <t>7,26; 12,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,03; 12,95</t>
+          <t>7,82; 12,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,34; 12,01</t>
+          <t>7,27; 12,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 12,99</t>
+          <t>2,98; 13,19</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,94%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>9,5%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>8,08%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>7,46%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,94%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,49; 15,82</t>
+          <t>3,21; 11,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 13,03</t>
+          <t>6,84; 16,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,5; 12,27</t>
+          <t>1,02; 6,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,26</t>
+          <t>0,99; 11,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 11,1</t>
+          <t>5,2; 15,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,67; 16,55</t>
+          <t>4,74; 12,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,25</t>
+          <t>4,23; 11,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 13,29</t>
+          <t>0,0; 11,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,94; 11,31</t>
+          <t>5,01; 11,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,77; 13,1</t>
+          <t>6,84; 12,89</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,65</t>
+          <t>3,18; 7,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 10,68</t>
+          <t>1,35; 9,06</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11,19%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10,25%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3,84%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>9,28%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>16,4%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12,84%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,19%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10,25%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,37</t>
+          <t>5,88; 18,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,89; 18,63</t>
+          <t>5,31; 17,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,72; 27,52</t>
+          <t>3,48; 15,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,02; 18,3</t>
+          <t>0,91; 9,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,24; 16,63</t>
+          <t>4,0; 17,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,43; 15,84</t>
+          <t>9,39; 26,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 36,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,45; 11,74</t>
+          <t>4,39; 12,06</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,97; 15,24</t>
+          <t>5,93; 14,63</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,7; 18,16</t>
+          <t>7,49; 18,15</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,53</t>
+          <t>0,0; 18,26</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8,48%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10,12%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8,63%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>8,68%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>9,91%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>9,67%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,12%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,63%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,95; 10,73</t>
+          <t>6,71; 10,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,11; 12,08</t>
+          <t>8,31; 12,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,82; 11,81</t>
+          <t>6,96; 10,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,89; 12,2</t>
+          <t>1,49; 7,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,84; 10,49</t>
+          <t>6,96; 10,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,42; 12,24</t>
+          <t>7,87; 11,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,93; 10,54</t>
+          <t>7,96; 11,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 7,05</t>
+          <t>3,63; 12,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,27; 9,83</t>
+          <t>7,32; 10,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,73; 11,39</t>
+          <t>8,74; 11,51</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,75; 10,47</t>
+          <t>7,84; 10,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,1</t>
+          <t>3,32; 8,1</t>
         </is>
       </c>
     </row>
@@ -1669,13 +1669,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
+          <t>Menores cuya última consulta médica fue por vacunación (tasa de respuesta: 98,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,37 +1791,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8237</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7450</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8523</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>11158</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>11205</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>6021</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1349</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8237</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7450</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8523</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2771</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6858; 17024</t>
+          <t>4182; 13561</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6115; 16992</t>
+          <t>4131; 12854</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2787; 11476</t>
+          <t>4389; 13547</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5278</t>
+          <t>0; 4671</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4447; 13212</t>
+          <t>6751; 17754</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3710; 13123</t>
+          <t>7001; 17926</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4894; 14163</t>
+          <t>3061; 10917</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4677</t>
+          <t>0; 5792</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13472; 27347</t>
+          <t>13154; 27661</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11994; 26612</t>
+          <t>12714; 25710</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9367; 22129</t>
+          <t>9219; 21210</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>832; 6676</t>
+          <t>793; 6823</t>
         </is>
       </c>
     </row>
@@ -1999,37 +1999,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2067,37 +2067,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6897</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10625</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9172</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6675</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7169</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>10815</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6897</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10625</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9172</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2135,17 +2135,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3546; 11325</t>
+          <t>3461; 11820</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3632; 12620</t>
+          <t>6192; 16258</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6345; 17284</t>
+          <t>4936; 14662</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2155,17 +2155,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3912; 12382</t>
+          <t>3605; 11453</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6320; 16399</t>
+          <t>3497; 12241</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5146; 14469</t>
+          <t>6491; 17021</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2175,17 +2175,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8956; 20470</t>
+          <t>8415; 19738</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12140; 25378</t>
+          <t>12195; 25166</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14283; 27664</t>
+          <t>13845; 27543</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2207,37 +2207,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5355</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6607</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9283</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>4168</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>8730</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>5524</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>763</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5355</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6607</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9283</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>734</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>982</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1566; 8831</t>
+          <t>2629; 9957</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4727; 14116</t>
+          <t>2981; 12126</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2847; 9802</t>
+          <t>5103; 14513</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2536</t>
+          <t>0; 1262</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2630; 10054</t>
+          <t>1440; 7655</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3287; 12142</t>
+          <t>4839; 13608</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5008; 14433</t>
+          <t>2750; 9407</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2221</t>
+          <t>0; 2491</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5594; 16174</t>
+          <t>5247; 14951</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9962; 22063</t>
+          <t>10279; 22470</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9467; 20972</t>
+          <t>9674; 21384</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3881</t>
+          <t>0; 3980</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>16236</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21993</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19386</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>15975</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>19727</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>18179</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3106</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16236</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21993</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>19386</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>4315</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10694; 22525</t>
+          <t>10912; 23304</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13562; 27520</t>
+          <t>15106; 29981</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12048; 25638</t>
+          <t>13730; 27491</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1111; 6567</t>
+          <t>277; 3515</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11456; 22813</t>
+          <t>11149; 23211</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15879; 30385</t>
+          <t>13075; 27509</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13636; 27442</t>
+          <t>11382; 25150</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3865</t>
+          <t>1075; 7018</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23901; 42702</t>
+          <t>25315; 42804</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32735; 52815</t>
+          <t>31896; 52481</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28899; 47328</t>
+          <t>28624; 47605</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1945; 9263</t>
+          <t>2013; 8898</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>6113</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>14395</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3518</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1162</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>8158</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>11013</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>9146</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6113</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>14395</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3518</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>598</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>1761</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4710; 13579</t>
+          <t>3292; 11514</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6842; 17756</t>
+          <t>9006; 21459</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5513; 15054</t>
+          <t>1304; 7825</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2711</t>
+          <t>273; 3170</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3303; 11400</t>
+          <t>4460; 13715</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8782; 21793</t>
+          <t>6455; 16840</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1317; 7972</t>
+          <t>5194; 14559</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>381; 3975</t>
+          <t>0; 2209</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9322; 21328</t>
+          <t>9440; 21706</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18136; 35099</t>
+          <t>18333; 34539</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7695; 19143</t>
+          <t>7960; 19859</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>820; 5375</t>
+          <t>640; 4290</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7426</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7126</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4982</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2638</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>4885</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>9233</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1201</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7426</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>7126</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4982</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1034</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>743; 6443</t>
+          <t>3906; 12258</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2048; 9811</t>
+          <t>3688; 12398</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4909; 15497</t>
+          <t>2122; 9418</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3626</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3995; 12144</t>
+          <t>628; 6578</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3643; 11558</t>
+          <t>2108; 9443</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2092; 9658</t>
+          <t>5285; 14923</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3490</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6012; 15864</t>
+          <t>5928; 16295</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7288; 18618</t>
+          <t>7249; 17868</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9032; 21299</t>
+          <t>8788; 21282</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 4106</t>
+          <t>0; 3666</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>50263</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>68196</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>54864</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4024</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>48772</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>62729</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>58918</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>7160</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>50263</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>68196</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>54864</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11846</t>
+          <t>10862</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>39060; 60277</t>
+          <t>39779; 61655</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>51326; 76480</t>
+          <t>56024; 82041</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47630; 71930</t>
+          <t>44269; 67634</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3839; 12035</t>
+          <t>1792; 8515</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>40555; 62147</t>
+          <t>39089; 61219</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>56715; 82447</t>
+          <t>49820; 75311</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44074; 67025</t>
+          <t>48507; 72646</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2281; 9189</t>
+          <t>3406; 11941</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>83884; 113481</t>
+          <t>84549; 116404</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>114088; 148906</t>
+          <t>114191; 150358</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>96503; 130409</t>
+          <t>97666; 130326</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7314; 18544</t>
+          <t>7123; 17379</t>
         </is>
       </c>
     </row>
